--- a/data/trans_dic/IP12B$otros-Clase-trans_dic.xlsx
+++ b/data/trans_dic/IP12B$otros-Clase-trans_dic.xlsx
@@ -7,7 +7,8 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Variables dicotomizadas" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Porcentajes" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Totales" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -523,7 +524,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores que han limitado su actividad por otros síntomas o dolor</t>
+          <t>Menores que han limitado su actividad por otros síntomas o dolor (tasa de respuesta: 99,36%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -677,47 +678,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 42,27</t>
+          <t>0,0; 40,74</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>0; 14,51</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 23,28</t>
+          <t>0,0; 32,8</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 45,26</t>
+          <t>0,0; 46,08</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 44,56</t>
+          <t>0,0; 44,87</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>0; 26,42</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>3,64; 31,15</t>
+          <t>3,62; 31,79</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 26,62</t>
+          <t>0,0; 18,88</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 18,52</t>
+          <t>0,0; 25,05</t>
         </is>
       </c>
     </row>
@@ -787,47 +788,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 43,08</t>
+          <t>0,0; 42,68</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>11,5; 55,48</t>
+          <t>10,85; 56,36</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>0; 23,25</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 53,02</t>
+          <t>0,0; 53,89</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 48,75</t>
+          <t>0,0; 48,42</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>0; 13,49</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 36,21</t>
+          <t>0,0; 35,99</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>10,93; 43,66</t>
+          <t>10,67; 43,37</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>0; 9,05</t>
+          <t>—; —</t>
         </is>
       </c>
     </row>
@@ -897,47 +898,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0; 23,25</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>0; 15,69</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 56,65</t>
+          <t>0,0; 57,48</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>9,41; 60,32</t>
+          <t>9,36; 60,31</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>0; 14,51</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 44,56</t>
+          <t>0,0; 59,12</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>5,8; 42,1</t>
+          <t>5,82; 42,89</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>0; 7,93</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 40,45</t>
+          <t>0,0; 42,12</t>
         </is>
       </c>
     </row>
@@ -1007,47 +1008,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 23,94</t>
+          <t>0,0; 22,34</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>7,25; 39,04</t>
+          <t>6,85; 37,14</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>3,61; 30,06</t>
+          <t>3,44; 28,25</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 25,82</t>
+          <t>0,0; 25,67</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>2,81; 22,37</t>
+          <t>2,79; 24,7</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>4,54; 37,07</t>
+          <t>4,86; 37,31</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>2,0; 15,44</t>
+          <t>2,05; 17,75</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>5,94; 24,76</t>
+          <t>6,3; 24,33</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>7,16; 26,53</t>
+          <t>7,04; 26,45</t>
         </is>
       </c>
     </row>
@@ -1117,47 +1118,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 34,34</t>
+          <t>0,0; 38,31</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 35,21</t>
+          <t>0,0; 30,3</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>6,03; 53,27</t>
+          <t>8,51; 56,3</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 51,29</t>
+          <t>0,0; 55,76</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 39,07</t>
+          <t>0,0; 38,02</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>0; 17,08</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 33,29</t>
+          <t>0,0; 30,21</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>2,8; 25,04</t>
+          <t>2,94; 27,18</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>4,57; 35,46</t>
+          <t>4,39; 34,95</t>
         </is>
       </c>
     </row>
@@ -1232,42 +1233,42 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>0; 36,25</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 78,7</t>
+          <t>0,0; 80,43</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>15,34; 83,15</t>
+          <t>15,42; 83,06</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 47,06</t>
+          <t>0,0; 48,18</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 67,59</t>
+          <t>0,0; 80,85</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>18,65; 79,39</t>
+          <t>18,14; 79,53</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 40,6</t>
+          <t>0,0; 37,63</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>7,92; 57,2</t>
+          <t>7,94; 63,9</t>
         </is>
       </c>
     </row>
@@ -1337,47 +1338,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>3,15; 17,79</t>
+          <t>3,34; 19,98</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>7,65; 22,52</t>
+          <t>7,92; 22,37</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>7,64; 22,77</t>
+          <t>7,73; 23,56</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>10,09; 27,83</t>
+          <t>10,1; 26,98</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>4,38; 17,27</t>
+          <t>4,14; 16,75</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>4,28; 20,04</t>
+          <t>4,35; 19,5</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>8,54; 20,32</t>
+          <t>8,73; 20,36</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>7,01; 17,19</t>
+          <t>7,2; 16,83</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>7,93; 18,86</t>
+          <t>7,9; 18,71</t>
         </is>
       </c>
     </row>
@@ -1404,4 +1405,1283 @@
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:K25"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="14" customWidth="1" min="1" max="1"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="14" customWidth="1" min="4" max="4"/>
+    <col width="14" customWidth="1" min="5" max="5"/>
+    <col width="14" customWidth="1" min="6" max="6"/>
+    <col width="14" customWidth="1" min="7" max="7"/>
+    <col width="14" customWidth="1" min="8" max="8"/>
+    <col width="14" customWidth="1" min="9" max="9"/>
+    <col width="14" customWidth="1" min="10" max="10"/>
+    <col width="14" customWidth="1" min="11" max="11"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Menores que han limitado su actividad por otros síntomas o dolor (tasa de respuesta: 99,36%)</t>
+        </is>
+      </c>
+      <c r="B1" s="2" t="n"/>
+      <c r="C1" s="3" t="inlineStr">
+        <is>
+          <t>Niña</t>
+        </is>
+      </c>
+      <c r="D1" s="3" t="n"/>
+      <c r="E1" s="3" t="n"/>
+      <c r="F1" s="3" t="inlineStr">
+        <is>
+          <t>Niño</t>
+        </is>
+      </c>
+      <c r="G1" s="3" t="n"/>
+      <c r="H1" s="3" t="n"/>
+      <c r="I1" s="3" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="J1" s="3" t="n"/>
+      <c r="K1" s="3" t="n"/>
+    </row>
+    <row r="2">
+      <c r="A2" s="4" t="n"/>
+      <c r="B2" s="2" t="n"/>
+      <c r="C2" s="3" t="inlineStr">
+        <is>
+          <t>2007</t>
+        </is>
+      </c>
+      <c r="D2" s="3" t="inlineStr">
+        <is>
+          <t>2012</t>
+        </is>
+      </c>
+      <c r="E2" s="3" t="inlineStr">
+        <is>
+          <t>2016</t>
+        </is>
+      </c>
+      <c r="F2" s="3" t="inlineStr">
+        <is>
+          <t>2007</t>
+        </is>
+      </c>
+      <c r="G2" s="3" t="inlineStr">
+        <is>
+          <t>2012</t>
+        </is>
+      </c>
+      <c r="H2" s="3" t="inlineStr">
+        <is>
+          <t>2016</t>
+        </is>
+      </c>
+      <c r="I2" s="3" t="inlineStr">
+        <is>
+          <t>2007</t>
+        </is>
+      </c>
+      <c r="J2" s="3" t="inlineStr">
+        <is>
+          <t>2012</t>
+        </is>
+      </c>
+      <c r="K2" s="3" t="inlineStr">
+        <is>
+          <t>2016</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" hidden="1">
+      <c r="A3" s="4" t="n"/>
+      <c r="B3" s="2" t="n"/>
+      <c r="C3" s="2" t="n"/>
+      <c r="D3" s="2" t="n"/>
+      <c r="E3" s="2" t="n"/>
+      <c r="F3" s="2" t="n"/>
+      <c r="G3" s="2" t="n"/>
+      <c r="H3" s="2" t="n"/>
+      <c r="I3" s="2" t="n"/>
+      <c r="J3" s="2" t="n"/>
+      <c r="K3" s="2" t="n"/>
+    </row>
+    <row r="4">
+      <c r="A4" s="1" t="inlineStr">
+        <is>
+          <t>Grupo I y II</t>
+        </is>
+      </c>
+      <c r="B4" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C4" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K4" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="1" t="n"/>
+      <c r="B5" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C5" s="2" t="inlineStr">
+        <is>
+          <t>527</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>544</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>1308</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>689</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>1835</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
+          <t>689</t>
+        </is>
+      </c>
+      <c r="K5" s="2" t="inlineStr">
+        <is>
+          <t>544</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="1" t="n"/>
+      <c r="B6" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C6" s="2" t="inlineStr">
+        <is>
+          <t>0; 2343</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>0; 3152</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>0; 3988</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>0; 2967</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>521; 4580</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
+          <t>0; 2879</t>
+        </is>
+      </c>
+      <c r="K6" s="2" t="inlineStr">
+        <is>
+          <t>0; 3404</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="1" t="inlineStr">
+        <is>
+          <t>Grupo III</t>
+        </is>
+      </c>
+      <c r="B7" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C7" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="K7" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="1" t="n"/>
+      <c r="B8" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C8" s="2" t="inlineStr">
+        <is>
+          <t>707</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>3572</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>832</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>652</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>1539</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
+          <t>4225</t>
+        </is>
+      </c>
+      <c r="K8" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="1" t="n"/>
+      <c r="B9" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C9" s="2" t="inlineStr">
+        <is>
+          <t>0; 2791</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>1317; 6841</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>0; 3265</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>0; 2704</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>0; 4534</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
+          <t>1891; 7686</t>
+        </is>
+      </c>
+      <c r="K9" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="1" t="inlineStr">
+        <is>
+          <t>Grupo IV y V</t>
+        </is>
+      </c>
+      <c r="B10" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C10" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K10" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="1" t="n"/>
+      <c r="B11" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C11" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>617</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>2024</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>636</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>2024</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K11" s="2" t="inlineStr">
+        <is>
+          <t>1253</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="1" t="n"/>
+      <c r="B12" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C12" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>0; 2605</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>643; 4142</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>0; 2974</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>654; 4816</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="K12" s="2" t="inlineStr">
+        <is>
+          <t>0; 4028</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="1" t="inlineStr">
+        <is>
+          <t>Grupo VI</t>
+        </is>
+      </c>
+      <c r="B13" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C13" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="K13" s="2" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="1" t="n"/>
+      <c r="B14" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C14" s="2" t="inlineStr">
+        <is>
+          <t>598</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>3353</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>2663</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>1283</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>2015</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>2932</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>1881</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
+          <t>5368</t>
+        </is>
+      </c>
+      <c r="K14" s="2" t="inlineStr">
+        <is>
+          <t>5595</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="1" t="n"/>
+      <c r="B15" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C15" s="2" t="inlineStr">
+        <is>
+          <t>0; 3089</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>1190; 6449</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>708; 5805</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>0; 3928</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>631; 5582</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>820; 6298</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>597; 5171</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
+          <t>2519; 9722</t>
+        </is>
+      </c>
+      <c r="K15" s="2" t="inlineStr">
+        <is>
+          <t>2635; 9901</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="1" t="inlineStr">
+        <is>
+          <t>Grupo VII</t>
+        </is>
+      </c>
+      <c r="B16" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C16" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="K16" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="1" t="n"/>
+      <c r="B17" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C17" s="2" t="inlineStr">
+        <is>
+          <t>632</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>1376</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>2785</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>808</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>1187</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>1440</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
+          <t>2563</t>
+        </is>
+      </c>
+      <c r="K17" s="2" t="inlineStr">
+        <is>
+          <t>2785</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="1" t="n"/>
+      <c r="B18" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C18" s="2" t="inlineStr">
+        <is>
+          <t>0; 3152</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>0; 3665</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>874; 5783</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>0; 3351</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>0; 3651</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>0; 4301</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
+          <t>637; 5896</t>
+        </is>
+      </c>
+      <c r="K18" s="2" t="inlineStr">
+        <is>
+          <t>778; 6188</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="1" t="inlineStr">
+        <is>
+          <t>No ha trabajado</t>
+        </is>
+      </c>
+      <c r="B19" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C19" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="D19" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E19" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="F19" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="G19" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H19" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="I19" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J19" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K19" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="1" t="n"/>
+      <c r="B20" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C20" s="2" t="inlineStr">
+        <is>
+          <t>1308</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="inlineStr">
+        <is>
+          <t>792</t>
+        </is>
+      </c>
+      <c r="F20" s="2" t="inlineStr">
+        <is>
+          <t>1851</t>
+        </is>
+      </c>
+      <c r="G20" s="2" t="inlineStr">
+        <is>
+          <t>744</t>
+        </is>
+      </c>
+      <c r="H20" s="2" t="inlineStr">
+        <is>
+          <t>1229</t>
+        </is>
+      </c>
+      <c r="I20" s="2" t="inlineStr">
+        <is>
+          <t>3159</t>
+        </is>
+      </c>
+      <c r="J20" s="2" t="inlineStr">
+        <is>
+          <t>744</t>
+        </is>
+      </c>
+      <c r="K20" s="2" t="inlineStr">
+        <is>
+          <t>2020</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="1" t="n"/>
+      <c r="B21" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C21" s="2" t="inlineStr">
+        <is>
+          <t>0; 2769</t>
+        </is>
+      </c>
+      <c r="D21" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="E21" s="2" t="inlineStr">
+        <is>
+          <t>0; 2739</t>
+        </is>
+      </c>
+      <c r="F21" s="2" t="inlineStr">
+        <is>
+          <t>587; 3165</t>
+        </is>
+      </c>
+      <c r="G21" s="2" t="inlineStr">
+        <is>
+          <t>0; 3083</t>
+        </is>
+      </c>
+      <c r="H21" s="2" t="inlineStr">
+        <is>
+          <t>0; 3142</t>
+        </is>
+      </c>
+      <c r="I21" s="2" t="inlineStr">
+        <is>
+          <t>1194; 5232</t>
+        </is>
+      </c>
+      <c r="J21" s="2" t="inlineStr">
+        <is>
+          <t>0; 3501</t>
+        </is>
+      </c>
+      <c r="K21" s="2" t="inlineStr">
+        <is>
+          <t>579; 4660</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="1" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="B22" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C22" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="E22" s="2" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="F22" s="2" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="G22" s="2" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="H22" s="2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="I22" s="2" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="J22" s="2" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="K22" s="2" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="1" t="n"/>
+      <c r="B23" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C23" s="2" t="inlineStr">
+        <is>
+          <t>3772</t>
+        </is>
+      </c>
+      <c r="D23" s="2" t="inlineStr">
+        <is>
+          <t>8301</t>
+        </is>
+      </c>
+      <c r="E23" s="2" t="inlineStr">
+        <is>
+          <t>7401</t>
+        </is>
+      </c>
+      <c r="F23" s="2" t="inlineStr">
+        <is>
+          <t>8106</t>
+        </is>
+      </c>
+      <c r="G23" s="2" t="inlineStr">
+        <is>
+          <t>5288</t>
+        </is>
+      </c>
+      <c r="H23" s="2" t="inlineStr">
+        <is>
+          <t>4796</t>
+        </is>
+      </c>
+      <c r="I23" s="2" t="inlineStr">
+        <is>
+          <t>11878</t>
+        </is>
+      </c>
+      <c r="J23" s="2" t="inlineStr">
+        <is>
+          <t>13589</t>
+        </is>
+      </c>
+      <c r="K23" s="2" t="inlineStr">
+        <is>
+          <t>12197</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="1" t="n"/>
+      <c r="B24" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C24" s="2" t="inlineStr">
+        <is>
+          <t>1387; 8288</t>
+        </is>
+      </c>
+      <c r="D24" s="2" t="inlineStr">
+        <is>
+          <t>4808; 13573</t>
+        </is>
+      </c>
+      <c r="E24" s="2" t="inlineStr">
+        <is>
+          <t>4082; 12440</t>
+        </is>
+      </c>
+      <c r="F24" s="2" t="inlineStr">
+        <is>
+          <t>4716; 12604</t>
+        </is>
+      </c>
+      <c r="G24" s="2" t="inlineStr">
+        <is>
+          <t>2430; 9821</t>
+        </is>
+      </c>
+      <c r="H24" s="2" t="inlineStr">
+        <is>
+          <t>1999; 8957</t>
+        </is>
+      </c>
+      <c r="I24" s="2" t="inlineStr">
+        <is>
+          <t>7694; 17953</t>
+        </is>
+      </c>
+      <c r="J24" s="2" t="inlineStr">
+        <is>
+          <t>8596; 20077</t>
+        </is>
+      </c>
+      <c r="K24" s="2" t="inlineStr">
+        <is>
+          <t>7802; 18476</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>Fuente: Encuesta Andaluza de Salud (menores)</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="11">
+    <mergeCell ref="C1:E1"/>
+    <mergeCell ref="A7:A9"/>
+    <mergeCell ref="A4:A6"/>
+    <mergeCell ref="A16:A18"/>
+    <mergeCell ref="A10:A12"/>
+    <mergeCell ref="F1:H1"/>
+    <mergeCell ref="I1:K1"/>
+    <mergeCell ref="A19:A21"/>
+    <mergeCell ref="A1:B2"/>
+    <mergeCell ref="A22:A24"/>
+    <mergeCell ref="A13:A15"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>
--- a/data/trans_dic/IP12B$otros-Clase-trans_dic.xlsx
+++ b/data/trans_dic/IP12B$otros-Clase-trans_dic.xlsx
@@ -524,7 +524,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores que han limitado su actividad por otros síntomas o dolor (tasa de respuesta: 99,36%)</t>
+          <t>Menores que en las últimas 2 semanas han limitado su actividad por otros síntomas o dolor (tasa de respuesta: 99,36%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -678,7 +678,7 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 40,74</t>
+          <t>0,0; 39,6</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
@@ -688,17 +688,17 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 32,8</t>
+          <t>0,0; 29,38</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 46,08</t>
+          <t>0,0; 39,35</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 44,87</t>
+          <t>0,0; 48,09</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
@@ -708,17 +708,17 @@
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>3,62; 31,79</t>
+          <t>3,56; 31,07</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 18,88</t>
+          <t>0,0; 18,71</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 25,05</t>
+          <t>0,0; 17,79</t>
         </is>
       </c>
     </row>
@@ -788,12 +788,12 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 42,68</t>
+          <t>0,0; 43,22</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>10,85; 56,36</t>
+          <t>11,66; 53,11</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
@@ -803,12 +803,12 @@
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 53,89</t>
+          <t>0,0; 61,73</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 48,42</t>
+          <t>0,0; 49,46</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
@@ -818,12 +818,12 @@
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 35,99</t>
+          <t>0,0; 35,94</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>10,67; 43,37</t>
+          <t>7,83; 42,05</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
@@ -908,12 +908,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 57,48</t>
+          <t>0,0; 60,59</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>9,36; 60,31</t>
+          <t>9,43; 60,25</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -923,12 +923,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 59,12</t>
+          <t>0,0; 55,57</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>5,82; 42,89</t>
+          <t>5,68; 42,16</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -938,7 +938,7 @@
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 42,12</t>
+          <t>0,0; 39,57</t>
         </is>
       </c>
     </row>
@@ -1008,47 +1008,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 22,34</t>
+          <t>0,0; 23,26</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>6,85; 37,14</t>
+          <t>7,17; 38,82</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>3,44; 28,25</t>
+          <t>3,51; 27,86</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 25,67</t>
+          <t>0,0; 25,6</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>2,79; 24,7</t>
+          <t>2,73; 24,28</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>4,86; 37,31</t>
+          <t>4,21; 36,17</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>2,05; 17,75</t>
+          <t>2,04; 16,52</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>6,3; 24,33</t>
+          <t>6,5; 24,46</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>7,04; 26,45</t>
+          <t>7,06; 26,42</t>
         </is>
       </c>
     </row>
@@ -1118,27 +1118,27 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 38,31</t>
+          <t>0,0; 34,54</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 30,3</t>
+          <t>0,0; 34,55</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>8,51; 56,3</t>
+          <t>8,56; 55,55</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 55,76</t>
+          <t>0,0; 51,3</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 38,02</t>
+          <t>0,0; 38,87</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
@@ -1148,17 +1148,17 @@
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 30,21</t>
+          <t>0,0; 30,7</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>2,94; 27,18</t>
+          <t>3,04; 27,67</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>4,39; 34,95</t>
+          <t>4,54; 35,23</t>
         </is>
       </c>
     </row>
@@ -1238,37 +1238,37 @@
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 80,43</t>
+          <t>0,0; 82,85</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>15,42; 83,06</t>
+          <t>15,53; 82,87</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 48,18</t>
+          <t>0,0; 48,01</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 80,85</t>
+          <t>0,0; 79,46</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>18,14; 79,53</t>
+          <t>18,67; 79,4</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 37,63</t>
+          <t>0,0; 33,09</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>7,94; 63,9</t>
+          <t>8,01; 62,45</t>
         </is>
       </c>
     </row>
@@ -1338,47 +1338,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>3,34; 19,98</t>
+          <t>4,22; 19,39</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>7,92; 22,37</t>
+          <t>7,59; 22,17</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>7,73; 23,56</t>
+          <t>7,38; 23,71</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>10,1; 26,98</t>
+          <t>9,46; 28,26</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>4,14; 16,75</t>
+          <t>4,34; 16,72</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>4,35; 19,5</t>
+          <t>4,2; 19,77</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>8,73; 20,36</t>
+          <t>8,38; 20,19</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>7,2; 16,83</t>
+          <t>7,38; 17,1</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>7,9; 18,71</t>
+          <t>7,43; 18,33</t>
         </is>
       </c>
     </row>
@@ -1432,7 +1432,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores que han limitado su actividad por otros síntomas o dolor (tasa de respuesta: 99,36%)</t>
+          <t>Menores que en las últimas 2 semanas han limitado su actividad por otros síntomas o dolor (tasa de respuesta: 99,36%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -1639,7 +1639,7 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>0; 2343</t>
+          <t>0; 2278</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
@@ -1649,17 +1649,17 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>0; 3152</t>
+          <t>0; 2824</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>0; 3988</t>
+          <t>0; 3405</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>0; 2967</t>
+          <t>0; 3180</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
@@ -1669,17 +1669,17 @@
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>521; 4580</t>
+          <t>513; 4477</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>0; 2879</t>
+          <t>0; 2853</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>0; 3404</t>
+          <t>0; 2418</t>
         </is>
       </c>
     </row>
@@ -1802,12 +1802,12 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0; 2791</t>
+          <t>0; 2826</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>1317; 6841</t>
+          <t>1415; 6446</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
@@ -1817,12 +1817,12 @@
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>0; 3265</t>
+          <t>0; 3740</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>0; 2704</t>
+          <t>0; 2762</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
@@ -1832,12 +1832,12 @@
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>0; 4534</t>
+          <t>0; 4527</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>1891; 7686</t>
+          <t>1388; 7453</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
@@ -1975,12 +1975,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>0; 2605</t>
+          <t>0; 2746</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>643; 4142</t>
+          <t>648; 4138</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1990,12 +1990,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>0; 2974</t>
+          <t>0; 2796</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>654; 4816</t>
+          <t>638; 4735</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -2005,7 +2005,7 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>0; 4028</t>
+          <t>0; 3784</t>
         </is>
       </c>
     </row>
@@ -2128,47 +2128,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>0; 3089</t>
+          <t>0; 3216</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>1190; 6449</t>
+          <t>1244; 6739</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>708; 5805</t>
+          <t>721; 5726</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>0; 3928</t>
+          <t>0; 3918</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>631; 5582</t>
+          <t>616; 5487</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>820; 6298</t>
+          <t>711; 6104</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>597; 5171</t>
+          <t>595; 4811</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>2519; 9722</t>
+          <t>2599; 9774</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>2635; 9901</t>
+          <t>2644; 9888</t>
         </is>
       </c>
     </row>
@@ -2291,27 +2291,27 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>0; 3152</t>
+          <t>0; 2841</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>0; 3665</t>
+          <t>0; 4178</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>874; 5783</t>
+          <t>880; 5706</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>0; 3351</t>
+          <t>0; 3083</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>0; 3651</t>
+          <t>0; 3733</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
@@ -2321,17 +2321,17 @@
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>0; 4301</t>
+          <t>0; 4371</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>637; 5896</t>
+          <t>659; 6003</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>778; 6188</t>
+          <t>804; 6238</t>
         </is>
       </c>
     </row>
@@ -2464,37 +2464,37 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>0; 2739</t>
+          <t>0; 2822</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>587; 3165</t>
+          <t>592; 3157</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>0; 3083</t>
+          <t>0; 3072</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>0; 3142</t>
+          <t>0; 3088</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>1194; 5232</t>
+          <t>1228; 5224</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>0; 3501</t>
+          <t>0; 3078</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>579; 4660</t>
+          <t>584; 4554</t>
         </is>
       </c>
     </row>
@@ -2617,47 +2617,47 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>1387; 8288</t>
+          <t>1748; 8041</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>4808; 13573</t>
+          <t>4607; 13454</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>4082; 12440</t>
+          <t>3895; 12519</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>4716; 12604</t>
+          <t>4420; 13198</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>2430; 9821</t>
+          <t>2545; 9805</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>1999; 8957</t>
+          <t>1930; 9082</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>7694; 17953</t>
+          <t>7386; 17802</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
         <is>
-          <t>8596; 20077</t>
+          <t>8805; 20400</t>
         </is>
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>7802; 18476</t>
+          <t>7335; 18101</t>
         </is>
       </c>
     </row>

--- a/data/trans_dic/IP12B$otros-Clase-trans_dic.xlsx
+++ b/data/trans_dic/IP12B$otros-Clase-trans_dic.xlsx
@@ -530,14 +530,14 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
       <c r="E1" s="3" t="n"/>
       <c r="F1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="G1" s="3" t="n"/>
@@ -625,32 +625,32 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>15,11%</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>10,41%</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
           <t>9,16%</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="G4" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
+      <c r="H4" s="2" t="inlineStr">
         <is>
           <t>5,66%</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>15,11%</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>10,41%</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
@@ -678,47 +678,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 39,6</t>
+          <t>0,0; 45,26</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
+          <t>0,0; 44,56</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
           <t>—; —</t>
         </is>
       </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>0,0; 29,38</t>
-        </is>
-      </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 39,35</t>
+          <t>0,0; 42,27</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 48,09</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>0,0; 23,28</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>3,56; 31,07</t>
+          <t>3,64; 31,15</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 18,71</t>
+          <t>0,0; 26,62</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 17,79</t>
+          <t>0,0; 18,52</t>
         </is>
       </c>
     </row>
@@ -735,27 +735,27 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>13,73%</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>11,68%</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
           <t>10,82%</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="G6" s="2" t="inlineStr">
         <is>
           <t>29,43%</t>
-        </is>
-      </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>13,73%</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>11,68%</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
@@ -788,12 +788,12 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 43,22</t>
+          <t>0,0; 53,02</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>11,66; 53,11</t>
+          <t>0,0; 48,75</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
@@ -803,12 +803,12 @@
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 61,73</t>
+          <t>0,0; 43,08</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 49,46</t>
+          <t>11,5; 55,48</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
@@ -818,12 +818,12 @@
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 35,94</t>
+          <t>0,0; 36,21</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>7,83; 42,05</t>
+          <t>10,93; 43,66</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
@@ -845,32 +845,32 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>29,48%</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>12,63%</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
         <is>
           <t>13,62%</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>29,48%</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>12,63%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -898,24 +898,24 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
+          <t>9,41; 60,32</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
           <t>—; —</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>0,0; 44,56</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
         <is>
           <t>—; —</t>
         </is>
       </c>
-      <c r="E9" s="2" t="inlineStr">
-        <is>
-          <t>0,0; 60,59</t>
-        </is>
-      </c>
-      <c r="F9" s="2" t="inlineStr">
-        <is>
-          <t>9,43; 60,25</t>
-        </is>
-      </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
           <t>—; —</t>
@@ -923,12 +923,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 55,57</t>
+          <t>0,0; 56,65</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>5,68; 42,16</t>
+          <t>5,8; 42,1</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -938,7 +938,7 @@
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 39,57</t>
+          <t>0,0; 40,45</t>
         </is>
       </c>
     </row>
@@ -955,32 +955,32 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>8,38%</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>8,92%</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>17,37%</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
           <t>4,32%</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="G10" s="2" t="inlineStr">
         <is>
           <t>19,31%</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
+      <c r="H10" s="2" t="inlineStr">
         <is>
           <t>12,96%</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>8,38%</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>8,92%</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>17,37%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
@@ -1008,47 +1008,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 23,26</t>
+          <t>0,0; 25,82</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>7,17; 38,82</t>
+          <t>2,81; 22,37</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>3,51; 27,86</t>
+          <t>4,54; 37,07</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 25,6</t>
+          <t>0,0; 23,94</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>2,73; 24,28</t>
+          <t>7,25; 39,04</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>4,21; 36,17</t>
+          <t>3,61; 30,06</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>2,04; 16,52</t>
+          <t>2,0; 15,44</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>6,5; 24,46</t>
+          <t>5,94; 24,76</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>7,06; 26,42</t>
+          <t>7,16; 26,53</t>
         </is>
       </c>
     </row>
@@ -1065,32 +1065,32 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>13,44%</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>12,36%</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
           <t>7,68%</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="G12" s="2" t="inlineStr">
         <is>
           <t>11,38%</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
+      <c r="H12" s="2" t="inlineStr">
         <is>
           <t>27,11%</t>
-        </is>
-      </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>13,44%</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>12,36%</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
@@ -1118,47 +1118,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 34,54</t>
+          <t>0,0; 51,29</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 34,55</t>
+          <t>0,0; 39,07</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>8,56; 55,55</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 51,3</t>
+          <t>0,0; 34,34</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 38,87</t>
+          <t>0,0; 35,21</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>6,03; 53,27</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 30,7</t>
+          <t>0,0; 33,29</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>3,04; 27,67</t>
+          <t>2,8; 25,04</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>4,54; 35,23</t>
+          <t>4,57; 35,46</t>
         </is>
       </c>
     </row>
@@ -1175,32 +1175,32 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>48,59%</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>11,63%</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>31,61%</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
           <t>47,23%</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="G14" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
+      <c r="H14" s="2" t="inlineStr">
         <is>
           <t>23,25%</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>48,59%</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
-        <is>
-          <t>11,63%</t>
-        </is>
-      </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>31,61%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -1228,47 +1228,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
+          <t>15,34; 83,15</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>0,0; 47,06</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>0,0; 67,59</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
           <t>0,0; 100,0</t>
         </is>
       </c>
-      <c r="D15" s="2" t="inlineStr">
+      <c r="G15" s="2" t="inlineStr">
         <is>
           <t>—; —</t>
         </is>
       </c>
-      <c r="E15" s="2" t="inlineStr">
-        <is>
-          <t>0,0; 82,85</t>
-        </is>
-      </c>
-      <c r="F15" s="2" t="inlineStr">
-        <is>
-          <t>15,53; 82,87</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>0,0; 48,01</t>
-        </is>
-      </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 79,46</t>
+          <t>0,0; 78,7</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>18,67; 79,4</t>
+          <t>18,65; 79,39</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 33,09</t>
+          <t>0,0; 40,6</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>8,01; 62,45</t>
+          <t>7,92; 57,2</t>
         </is>
       </c>
     </row>
@@ -1285,32 +1285,32 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>17,36%</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>9,02%</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>10,44%</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
           <t>9,09%</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
+      <c r="G16" s="2" t="inlineStr">
         <is>
           <t>13,68%</t>
         </is>
       </c>
-      <c r="E16" s="2" t="inlineStr">
+      <c r="H16" s="2" t="inlineStr">
         <is>
           <t>14,02%</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>17,36%</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
-        <is>
-          <t>9,02%</t>
-        </is>
-      </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>10,44%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
@@ -1338,47 +1338,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>4,22; 19,39</t>
+          <t>10,09; 27,83</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>7,59; 22,17</t>
+          <t>4,38; 17,27</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>7,38; 23,71</t>
+          <t>4,28; 20,04</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>9,46; 28,26</t>
+          <t>3,15; 17,79</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>4,34; 16,72</t>
+          <t>7,65; 22,52</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>4,2; 19,77</t>
+          <t>7,64; 22,77</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>8,38; 20,19</t>
+          <t>8,54; 20,32</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>7,38; 17,1</t>
+          <t>7,01; 17,19</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>7,43; 18,33</t>
+          <t>7,93; 18,86</t>
         </is>
       </c>
     </row>
@@ -1438,14 +1438,14 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
       <c r="E1" s="3" t="n"/>
       <c r="F1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="G1" s="3" t="n"/>
@@ -1533,32 +1533,32 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="E4" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
+      <c r="F4" s="2" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
           <t>1</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
@@ -1586,32 +1586,32 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>1308</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>689</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
           <t>527</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="G5" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="E5" s="2" t="inlineStr">
+      <c r="H5" s="2" t="inlineStr">
         <is>
           <t>544</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>1308</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
-        <is>
-          <t>689</t>
-        </is>
-      </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
@@ -1639,47 +1639,47 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>0; 2278</t>
+          <t>0; 3917</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
+          <t>0; 2947</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
           <t>—; —</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>0; 2824</t>
-        </is>
-      </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>0; 3405</t>
+          <t>0; 2431</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>0; 3180</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>0; 2238</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>513; 4477</t>
+          <t>525; 4488</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>0; 2853</t>
+          <t>0; 4059</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>0; 2418</t>
+          <t>0; 2517</t>
         </is>
       </c>
     </row>
@@ -1701,22 +1701,22 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
           <t>5</t>
-        </is>
-      </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
@@ -1749,27 +1749,27 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>832</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>652</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
           <t>707</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="G8" s="2" t="inlineStr">
         <is>
           <t>3572</t>
-        </is>
-      </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>832</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>652</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
@@ -1802,12 +1802,12 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0; 2826</t>
+          <t>0; 3212</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>1415; 6446</t>
+          <t>0; 2722</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
@@ -1817,12 +1817,12 @@
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>0; 3740</t>
+          <t>0; 2817</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>0; 2762</t>
+          <t>1396; 6734</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
@@ -1832,12 +1832,12 @@
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>0; 4527</t>
+          <t>0; 4561</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>1388; 7453</t>
+          <t>1937; 7738</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
@@ -1859,22 +1859,22 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
         <is>
           <t>0</t>
-        </is>
-      </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1912,32 +1912,32 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>2024</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>636</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="E11" s="2" t="inlineStr">
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
         <is>
           <t>617</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>2024</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>636</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
@@ -1965,24 +1965,24 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>647; 4143</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
           <t>—; —</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>0; 2242</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
         <is>
           <t>—; —</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>0; 2746</t>
-        </is>
-      </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>648; 4138</t>
-        </is>
-      </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
           <t>—; —</t>
@@ -1990,12 +1990,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>0; 2796</t>
+          <t>0; 2567</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>638; 4735</t>
+          <t>651; 4727</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -2005,7 +2005,7 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>0; 3784</t>
+          <t>0; 3868</t>
         </is>
       </c>
     </row>
@@ -2022,27 +2022,27 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
+      <c r="G13" s="2" t="inlineStr">
         <is>
           <t>5</t>
-        </is>
-      </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
@@ -2075,32 +2075,32 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>1283</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>2015</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>2932</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
           <t>598</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="G14" s="2" t="inlineStr">
         <is>
           <t>3353</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
+      <c r="H14" s="2" t="inlineStr">
         <is>
           <t>2663</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>1283</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
-        <is>
-          <t>2015</t>
-        </is>
-      </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>2932</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -2128,47 +2128,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>0; 3216</t>
+          <t>0; 3952</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>1244; 6739</t>
+          <t>636; 5055</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>721; 5726</t>
+          <t>767; 6256</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>0; 3918</t>
+          <t>0; 3311</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>616; 5487</t>
+          <t>1258; 6777</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>711; 6104</t>
+          <t>742; 6178</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>595; 4811</t>
+          <t>582; 4498</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>2599; 9774</t>
+          <t>2373; 9895</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>2644; 9888</t>
+          <t>2679; 9930</t>
         </is>
       </c>
     </row>
@@ -2195,22 +2195,22 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
           <t>4</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
@@ -2238,32 +2238,32 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
+          <t>808</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>1187</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
           <t>632</t>
         </is>
       </c>
-      <c r="D17" s="2" t="inlineStr">
+      <c r="G17" s="2" t="inlineStr">
         <is>
           <t>1376</t>
         </is>
       </c>
-      <c r="E17" s="2" t="inlineStr">
+      <c r="H17" s="2" t="inlineStr">
         <is>
           <t>2785</t>
-        </is>
-      </c>
-      <c r="F17" s="2" t="inlineStr">
-        <is>
-          <t>808</t>
-        </is>
-      </c>
-      <c r="G17" s="2" t="inlineStr">
-        <is>
-          <t>1187</t>
-        </is>
-      </c>
-      <c r="H17" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
@@ -2291,47 +2291,47 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>0; 2841</t>
+          <t>0; 3083</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>0; 4178</t>
+          <t>0; 3752</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>880; 5706</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>0; 3083</t>
+          <t>0; 2825</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>0; 3733</t>
+          <t>0; 4258</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>619; 5472</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>0; 4371</t>
+          <t>0; 4740</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>659; 6003</t>
+          <t>607; 5432</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>804; 6238</t>
+          <t>809; 6278</t>
         </is>
       </c>
     </row>
@@ -2348,32 +2348,32 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="D19" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="E19" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="D19" s="2" t="inlineStr">
+      <c r="F19" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="G19" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="E19" s="2" t="inlineStr">
+      <c r="H19" s="2" t="inlineStr">
         <is>
           <t>1</t>
-        </is>
-      </c>
-      <c r="F19" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="G19" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="H19" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
@@ -2401,32 +2401,32 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
+          <t>1851</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
+        <is>
+          <t>744</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="inlineStr">
+        <is>
+          <t>1229</t>
+        </is>
+      </c>
+      <c r="F20" s="2" t="inlineStr">
+        <is>
           <t>1308</t>
         </is>
       </c>
-      <c r="D20" s="2" t="inlineStr">
+      <c r="G20" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="E20" s="2" t="inlineStr">
+      <c r="H20" s="2" t="inlineStr">
         <is>
           <t>792</t>
-        </is>
-      </c>
-      <c r="F20" s="2" t="inlineStr">
-        <is>
-          <t>1851</t>
-        </is>
-      </c>
-      <c r="G20" s="2" t="inlineStr">
-        <is>
-          <t>744</t>
-        </is>
-      </c>
-      <c r="H20" s="2" t="inlineStr">
-        <is>
-          <t>1229</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
@@ -2454,47 +2454,47 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
+          <t>585; 3168</t>
+        </is>
+      </c>
+      <c r="D21" s="2" t="inlineStr">
+        <is>
+          <t>0; 3011</t>
+        </is>
+      </c>
+      <c r="E21" s="2" t="inlineStr">
+        <is>
+          <t>0; 2626</t>
+        </is>
+      </c>
+      <c r="F21" s="2" t="inlineStr">
+        <is>
           <t>0; 2769</t>
         </is>
       </c>
-      <c r="D21" s="2" t="inlineStr">
+      <c r="G21" s="2" t="inlineStr">
         <is>
           <t>—; —</t>
         </is>
       </c>
-      <c r="E21" s="2" t="inlineStr">
-        <is>
-          <t>0; 2822</t>
-        </is>
-      </c>
-      <c r="F21" s="2" t="inlineStr">
-        <is>
-          <t>592; 3157</t>
-        </is>
-      </c>
-      <c r="G21" s="2" t="inlineStr">
-        <is>
-          <t>0; 3072</t>
-        </is>
-      </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>0; 3088</t>
+          <t>0; 2680</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>1228; 5224</t>
+          <t>1227; 5223</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>0; 3078</t>
+          <t>0; 3778</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>584; 4554</t>
+          <t>577; 4171</t>
         </is>
       </c>
     </row>
@@ -2511,32 +2511,32 @@
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="E22" s="2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="F22" s="2" t="inlineStr">
+        <is>
           <t>6</t>
         </is>
       </c>
-      <c r="D22" s="2" t="inlineStr">
+      <c r="G22" s="2" t="inlineStr">
         <is>
           <t>12</t>
         </is>
       </c>
-      <c r="E22" s="2" t="inlineStr">
+      <c r="H22" s="2" t="inlineStr">
         <is>
           <t>11</t>
-        </is>
-      </c>
-      <c r="F22" s="2" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="G22" s="2" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="H22" s="2" t="inlineStr">
-        <is>
-          <t>7</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
@@ -2564,32 +2564,32 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
+          <t>8106</t>
+        </is>
+      </c>
+      <c r="D23" s="2" t="inlineStr">
+        <is>
+          <t>5288</t>
+        </is>
+      </c>
+      <c r="E23" s="2" t="inlineStr">
+        <is>
+          <t>4796</t>
+        </is>
+      </c>
+      <c r="F23" s="2" t="inlineStr">
+        <is>
           <t>3772</t>
         </is>
       </c>
-      <c r="D23" s="2" t="inlineStr">
+      <c r="G23" s="2" t="inlineStr">
         <is>
           <t>8301</t>
         </is>
       </c>
-      <c r="E23" s="2" t="inlineStr">
+      <c r="H23" s="2" t="inlineStr">
         <is>
           <t>7401</t>
-        </is>
-      </c>
-      <c r="F23" s="2" t="inlineStr">
-        <is>
-          <t>8106</t>
-        </is>
-      </c>
-      <c r="G23" s="2" t="inlineStr">
-        <is>
-          <t>5288</t>
-        </is>
-      </c>
-      <c r="H23" s="2" t="inlineStr">
-        <is>
-          <t>4796</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
@@ -2617,47 +2617,47 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>1748; 8041</t>
+          <t>4714; 12997</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>4607; 13454</t>
+          <t>2571; 10129</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>3895; 12519</t>
+          <t>1967; 9208</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>4420; 13198</t>
+          <t>1308; 7380</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>2545; 9805</t>
+          <t>4640; 13667</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>1930; 9082</t>
+          <t>4035; 12020</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>7386; 17802</t>
+          <t>7526; 17920</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
         <is>
-          <t>8805; 20400</t>
+          <t>8367; 20515</t>
         </is>
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>7335; 18101</t>
+          <t>7830; 18626</t>
         </is>
       </c>
     </row>
